--- a/alligator_data_2.0.xlsx
+++ b/alligator_data_2.0.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2713"/>
+  <dimension ref="A1:F2807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -63935,7 +63935,2178 @@
       <c r="E2713" t="n">
         <v>13</v>
       </c>
-      <c r="F2713" t="inlineStr"/>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:07</t>
+        </is>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2714" t="n">
+        <v>51</v>
+      </c>
+      <c r="E2714" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:15</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2715" t="n">
+        <v>1.14184</v>
+      </c>
+      <c r="E2715" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:17</t>
+        </is>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2716" t="n">
+        <v>0.60456</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:19</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2717" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:21</t>
+        </is>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2718" t="n">
+        <v>0.82159</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:23</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2719" t="n">
+        <v>144.655</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:28</t>
+        </is>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.93818</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:32</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.35154</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:35</t>
+        </is>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.36926</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:38</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2723" t="n">
+        <v>165.19</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:42</t>
+        </is>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2724" t="n">
+        <v>0.89241</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:48</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2725" t="n">
+        <v>0.65169</v>
+      </c>
+      <c r="E2725" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:52</t>
+        </is>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2726" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:53</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.53545</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:55</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2728" t="n">
+        <v>176.055</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:30:59</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:03</t>
+        </is>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2730" t="n">
+        <v>1.1105</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:06</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2731" t="n">
+        <v>1.56344</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:11</t>
+        </is>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.85064</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:15</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2733" t="n">
+        <v>3328.39</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:17</t>
+        </is>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2734" t="n">
+        <v>195.516</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:19</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2735" t="n">
+        <v>36.5542</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:31:21</t>
+        </is>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.28614</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:07</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2737" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:15</t>
+        </is>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.14184</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:17</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.60456</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:19</t>
+        </is>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:21</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2741" t="n">
+        <v>0.82159</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:23</t>
+        </is>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2742" t="n">
+        <v>144.655</v>
+      </c>
+      <c r="E2742" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:25</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.93818</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:27</t>
+        </is>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.35154</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:30</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.36926</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:32</t>
+        </is>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2746" t="n">
+        <v>165.19</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:34</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.89241</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:37</t>
+        </is>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.65169</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:38</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2749" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:40</t>
+        </is>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.53545</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:44</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2751" t="n">
+        <v>176.055</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:46</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2752" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:48</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2753" t="n">
+        <v>1.1105</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:51</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2754" t="n">
+        <v>1.56344</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:54</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2755" t="n">
+        <v>1.85064</v>
+      </c>
+      <c r="E2755" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:56</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2756" t="n">
+        <v>3328.39</v>
+      </c>
+      <c r="E2756" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:40:59</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2757" t="n">
+        <v>195.516</v>
+      </c>
+      <c r="E2757" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:41:01</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2758" t="n">
+        <v>36.5542</v>
+      </c>
+      <c r="E2758" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:41:03</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2759" t="n">
+        <v>1.28614</v>
+      </c>
+      <c r="E2759" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:43:56</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2760" t="n">
+        <v>1.56344</v>
+      </c>
+      <c r="E2760" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F2760" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:07</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2761" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2761" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:10</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2762" t="n">
+        <v>1.14184</v>
+      </c>
+      <c r="E2762" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:12</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2763" t="n">
+        <v>0.60456</v>
+      </c>
+      <c r="E2763" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:15</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2764" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="E2764" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:16</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2765" t="n">
+        <v>0.82159</v>
+      </c>
+      <c r="E2765" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:18</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2766" t="n">
+        <v>144.655</v>
+      </c>
+      <c r="E2766" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:20</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2767" t="n">
+        <v>0.93818</v>
+      </c>
+      <c r="E2767" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:22</t>
+        </is>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2768" t="n">
+        <v>1.35154</v>
+      </c>
+      <c r="E2768" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:24</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2769" t="n">
+        <v>1.36926</v>
+      </c>
+      <c r="E2769" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:26</t>
+        </is>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2770" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2770" t="n">
+        <v>165.19</v>
+      </c>
+      <c r="E2770" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:28</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2771" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2771" t="n">
+        <v>0.89241</v>
+      </c>
+      <c r="E2771" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:30</t>
+        </is>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2772" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2772" t="n">
+        <v>0.65169</v>
+      </c>
+      <c r="E2772" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:32</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2773" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="E2773" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:34</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2774" t="n">
+        <v>0.53545</v>
+      </c>
+      <c r="E2774" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:37</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2775" t="n">
+        <v>176.055</v>
+      </c>
+      <c r="E2775" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:38</t>
+        </is>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2776" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2776" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2776" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:41</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2777" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2777" t="n">
+        <v>1.1105</v>
+      </c>
+      <c r="E2777" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:43</t>
+        </is>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2778" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2778" t="n">
+        <v>1.56344</v>
+      </c>
+      <c r="E2778" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:45</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2779" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2779" t="n">
+        <v>1.85064</v>
+      </c>
+      <c r="E2779" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:48</t>
+        </is>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2780" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2780" t="n">
+        <v>3328.39</v>
+      </c>
+      <c r="E2780" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:50</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2781" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2781" t="n">
+        <v>195.516</v>
+      </c>
+      <c r="E2781" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:52</t>
+        </is>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2782" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2782" t="n">
+        <v>36.5542</v>
+      </c>
+      <c r="E2782" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>2025-06-10 20:50:54</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2783" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2783" t="n">
+        <v>1.28614</v>
+      </c>
+      <c r="E2783" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:08</t>
+        </is>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2784" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2784" t="n">
+        <v>44</v>
+      </c>
+      <c r="E2784" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:32</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2785" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2785" t="n">
+        <v>1.14187</v>
+      </c>
+      <c r="E2785" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:34</t>
+        </is>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2786" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2786" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="E2786" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:36</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2787" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2787" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="E2787" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:38</t>
+        </is>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2788" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2788" t="n">
+        <v>0.8216599999999999</v>
+      </c>
+      <c r="E2788" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:39</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2789" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2789" t="n">
+        <v>144.692</v>
+      </c>
+      <c r="E2789" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:41</t>
+        </is>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2790" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2790" t="n">
+        <v>0.93829</v>
+      </c>
+      <c r="E2790" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:43</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2791" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2791" t="n">
+        <v>1.35138</v>
+      </c>
+      <c r="E2791" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:45</t>
+        </is>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2792" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2792" t="n">
+        <v>1.36909</v>
+      </c>
+      <c r="E2792" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:46</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2793" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2793" t="n">
+        <v>165.234</v>
+      </c>
+      <c r="E2793" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:48</t>
+        </is>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2794" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2794" t="n">
+        <v>0.89233</v>
+      </c>
+      <c r="E2794" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:50</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2795" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2795" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E2795" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:52</t>
+        </is>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2796" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2796" t="n">
+        <v>94.307</v>
+      </c>
+      <c r="E2796" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:54</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2797" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2797" t="n">
+        <v>0.53552</v>
+      </c>
+      <c r="E2797" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:56</t>
+        </is>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2798" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2798" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E2798" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:00:58</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2799" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2799" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2799" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:00</t>
+        </is>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2800" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2800" t="n">
+        <v>1.11048</v>
+      </c>
+      <c r="E2800" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:02</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2801" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2801" t="n">
+        <v>1.56328</v>
+      </c>
+      <c r="E2801" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:04</t>
+        </is>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2802" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2802" t="n">
+        <v>1.85021</v>
+      </c>
+      <c r="E2802" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:06</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2803" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2803" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="E2803" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:07</t>
+        </is>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2804" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2804" t="n">
+        <v>195.543</v>
+      </c>
+      <c r="E2804" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:09</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2805" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2805" t="n">
+        <v>36.5429</v>
+      </c>
+      <c r="E2805" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:01:10</t>
+        </is>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2806" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2806" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="E2806" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:03:57</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C2807" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2807" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E2807" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F2807" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/alligator_data_2.0.xlsx
+++ b/alligator_data_2.0.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2807"/>
+  <dimension ref="A1:F3138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -66108,6 +66108,7645 @@
         </is>
       </c>
     </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:10:07</t>
+        </is>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2808" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2808" t="n">
+        <v>1.85021</v>
+      </c>
+      <c r="E2808" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:10:09</t>
+        </is>
+      </c>
+      <c r="B2809" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2809" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2809" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="E2809" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:10:11</t>
+        </is>
+      </c>
+      <c r="B2810" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2810" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2810" t="n">
+        <v>195.543</v>
+      </c>
+      <c r="E2810" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:10:14</t>
+        </is>
+      </c>
+      <c r="B2811" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2811" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2811" t="n">
+        <v>36.5429</v>
+      </c>
+      <c r="E2811" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:10:17</t>
+        </is>
+      </c>
+      <c r="B2812" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2812" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2812" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="E2812" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:29</t>
+        </is>
+      </c>
+      <c r="B2813" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2813" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2813" t="n">
+        <v>1.14187</v>
+      </c>
+      <c r="E2813" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:31</t>
+        </is>
+      </c>
+      <c r="B2814" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2814" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2814" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="E2814" t="n">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:32</t>
+        </is>
+      </c>
+      <c r="B2815" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2815" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2815" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="E2815" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:33</t>
+        </is>
+      </c>
+      <c r="B2816" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2816" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2816" t="n">
+        <v>0.8216599999999999</v>
+      </c>
+      <c r="E2816" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:35</t>
+        </is>
+      </c>
+      <c r="B2817" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2817" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2817" t="n">
+        <v>144.692</v>
+      </c>
+      <c r="E2817" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:38</t>
+        </is>
+      </c>
+      <c r="B2818" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2818" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2818" t="n">
+        <v>0.93829</v>
+      </c>
+      <c r="E2818" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:39</t>
+        </is>
+      </c>
+      <c r="B2819" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2819" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2819" t="n">
+        <v>1.35138</v>
+      </c>
+      <c r="E2819" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:41</t>
+        </is>
+      </c>
+      <c r="B2820" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2820" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2820" t="n">
+        <v>1.36909</v>
+      </c>
+      <c r="E2820" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:42</t>
+        </is>
+      </c>
+      <c r="B2821" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2821" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2821" t="n">
+        <v>165.234</v>
+      </c>
+      <c r="E2821" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:44</t>
+        </is>
+      </c>
+      <c r="B2822" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2822" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2822" t="n">
+        <v>0.89233</v>
+      </c>
+      <c r="E2822" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:46</t>
+        </is>
+      </c>
+      <c r="B2823" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2823" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2823" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E2823" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:48</t>
+        </is>
+      </c>
+      <c r="B2824" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2824" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2824" t="n">
+        <v>94.307</v>
+      </c>
+      <c r="E2824" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:49</t>
+        </is>
+      </c>
+      <c r="B2825" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2825" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2825" t="n">
+        <v>0.53552</v>
+      </c>
+      <c r="E2825" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:51</t>
+        </is>
+      </c>
+      <c r="B2826" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2826" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2826" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E2826" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:52</t>
+        </is>
+      </c>
+      <c r="B2827" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2827" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2827" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2827" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:54</t>
+        </is>
+      </c>
+      <c r="B2828" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2828" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2828" t="n">
+        <v>1.11048</v>
+      </c>
+      <c r="E2828" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:55</t>
+        </is>
+      </c>
+      <c r="B2829" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2829" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2829" t="n">
+        <v>1.56328</v>
+      </c>
+      <c r="E2829" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:57</t>
+        </is>
+      </c>
+      <c r="B2830" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2830" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2830" t="n">
+        <v>1.85021</v>
+      </c>
+      <c r="E2830" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:20:58</t>
+        </is>
+      </c>
+      <c r="B2831" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2831" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2831" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="E2831" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:21:00</t>
+        </is>
+      </c>
+      <c r="B2832" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2832" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2832" t="n">
+        <v>195.543</v>
+      </c>
+      <c r="E2832" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:21:01</t>
+        </is>
+      </c>
+      <c r="B2833" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2833" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2833" t="n">
+        <v>36.5429</v>
+      </c>
+      <c r="E2833" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:21:03</t>
+        </is>
+      </c>
+      <c r="B2834" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2834" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2834" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="E2834" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:35</t>
+        </is>
+      </c>
+      <c r="B2835" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2835" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2835" t="n">
+        <v>1.14187</v>
+      </c>
+      <c r="E2835" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:36</t>
+        </is>
+      </c>
+      <c r="B2836" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2836" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2836" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="E2836" t="n">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:38</t>
+        </is>
+      </c>
+      <c r="B2837" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2837" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2837" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="E2837" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:39</t>
+        </is>
+      </c>
+      <c r="B2838" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2838" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2838" t="n">
+        <v>0.8216599999999999</v>
+      </c>
+      <c r="E2838" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:41</t>
+        </is>
+      </c>
+      <c r="B2839" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2839" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2839" t="n">
+        <v>144.692</v>
+      </c>
+      <c r="E2839" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:43</t>
+        </is>
+      </c>
+      <c r="B2840" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2840" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2840" t="n">
+        <v>0.93829</v>
+      </c>
+      <c r="E2840" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:44</t>
+        </is>
+      </c>
+      <c r="B2841" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2841" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2841" t="n">
+        <v>1.35138</v>
+      </c>
+      <c r="E2841" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:46</t>
+        </is>
+      </c>
+      <c r="B2842" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2842" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2842" t="n">
+        <v>1.36909</v>
+      </c>
+      <c r="E2842" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:47</t>
+        </is>
+      </c>
+      <c r="B2843" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2843" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2843" t="n">
+        <v>165.234</v>
+      </c>
+      <c r="E2843" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:49</t>
+        </is>
+      </c>
+      <c r="B2844" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2844" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2844" t="n">
+        <v>0.89233</v>
+      </c>
+      <c r="E2844" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:50</t>
+        </is>
+      </c>
+      <c r="B2845" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2845" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2845" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E2845" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:52</t>
+        </is>
+      </c>
+      <c r="B2846" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2846" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2846" t="n">
+        <v>94.307</v>
+      </c>
+      <c r="E2846" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:53</t>
+        </is>
+      </c>
+      <c r="B2847" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2847" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2847" t="n">
+        <v>0.53552</v>
+      </c>
+      <c r="E2847" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:55</t>
+        </is>
+      </c>
+      <c r="B2848" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2848" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2848" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E2848" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:56</t>
+        </is>
+      </c>
+      <c r="B2849" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2849" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2849" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2849" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:30:58</t>
+        </is>
+      </c>
+      <c r="B2850" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2850" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2850" t="n">
+        <v>1.11048</v>
+      </c>
+      <c r="E2850" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:31:00</t>
+        </is>
+      </c>
+      <c r="B2851" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2851" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2851" t="n">
+        <v>1.56328</v>
+      </c>
+      <c r="E2851" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:31:01</t>
+        </is>
+      </c>
+      <c r="B2852" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2852" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2852" t="n">
+        <v>1.85021</v>
+      </c>
+      <c r="E2852" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:31:03</t>
+        </is>
+      </c>
+      <c r="B2853" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2853" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2853" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="E2853" t="n">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:31:05</t>
+        </is>
+      </c>
+      <c r="B2854" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2854" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2854" t="n">
+        <v>195.543</v>
+      </c>
+      <c r="E2854" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:31:07</t>
+        </is>
+      </c>
+      <c r="B2855" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2855" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2855" t="n">
+        <v>36.5429</v>
+      </c>
+      <c r="E2855" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:31:09</t>
+        </is>
+      </c>
+      <c r="B2856" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2856" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2856" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="E2856" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:07</t>
+        </is>
+      </c>
+      <c r="B2857" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2857" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2857" t="n">
+        <v>1.14187</v>
+      </c>
+      <c r="E2857" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:09</t>
+        </is>
+      </c>
+      <c r="B2858" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2858" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2858" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="E2858" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:12</t>
+        </is>
+      </c>
+      <c r="B2859" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2859" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2859" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="E2859" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:19</t>
+        </is>
+      </c>
+      <c r="B2860" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2860" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2860" t="n">
+        <v>0.8216599999999999</v>
+      </c>
+      <c r="E2860" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:23</t>
+        </is>
+      </c>
+      <c r="B2861" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2861" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2861" t="n">
+        <v>144.692</v>
+      </c>
+      <c r="E2861" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:26</t>
+        </is>
+      </c>
+      <c r="B2862" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2862" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2862" t="n">
+        <v>0.93829</v>
+      </c>
+      <c r="E2862" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:29</t>
+        </is>
+      </c>
+      <c r="B2863" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2863" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2863" t="n">
+        <v>1.35138</v>
+      </c>
+      <c r="E2863" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:33</t>
+        </is>
+      </c>
+      <c r="B2864" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2864" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2864" t="n">
+        <v>1.36909</v>
+      </c>
+      <c r="E2864" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:37</t>
+        </is>
+      </c>
+      <c r="B2865" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2865" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2865" t="n">
+        <v>165.234</v>
+      </c>
+      <c r="E2865" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:42</t>
+        </is>
+      </c>
+      <c r="B2866" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2866" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2866" t="n">
+        <v>0.89233</v>
+      </c>
+      <c r="E2866" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:46</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2867" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2867" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E2867" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:50</t>
+        </is>
+      </c>
+      <c r="B2868" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2868" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2868" t="n">
+        <v>94.307</v>
+      </c>
+      <c r="E2868" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:54</t>
+        </is>
+      </c>
+      <c r="B2869" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2869" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2869" t="n">
+        <v>0.53552</v>
+      </c>
+      <c r="E2869" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:40:58</t>
+        </is>
+      </c>
+      <c r="B2870" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2870" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2870" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E2870" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:04</t>
+        </is>
+      </c>
+      <c r="B2871" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2871" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2871" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2871" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:07</t>
+        </is>
+      </c>
+      <c r="B2872" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2872" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2872" t="n">
+        <v>1.11048</v>
+      </c>
+      <c r="E2872" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:10</t>
+        </is>
+      </c>
+      <c r="B2873" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2873" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2873" t="n">
+        <v>1.56328</v>
+      </c>
+      <c r="E2873" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:13</t>
+        </is>
+      </c>
+      <c r="B2874" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2874" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2874" t="n">
+        <v>1.85021</v>
+      </c>
+      <c r="E2874" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:15</t>
+        </is>
+      </c>
+      <c r="B2875" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2875" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2875" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="E2875" t="n">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:17</t>
+        </is>
+      </c>
+      <c r="B2876" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2876" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2876" t="n">
+        <v>195.543</v>
+      </c>
+      <c r="E2876" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:20</t>
+        </is>
+      </c>
+      <c r="B2877" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2877" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2877" t="n">
+        <v>36.5429</v>
+      </c>
+      <c r="E2877" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:41:22</t>
+        </is>
+      </c>
+      <c r="B2878" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2878" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2878" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="E2878" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:42:54</t>
+        </is>
+      </c>
+      <c r="B2879" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2879" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2879" t="n">
+        <v>43</v>
+      </c>
+      <c r="E2879" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:43:19</t>
+        </is>
+      </c>
+      <c r="B2880" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2880" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2880" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2880" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:43:39</t>
+        </is>
+      </c>
+      <c r="B2881" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2881" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2881" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2881" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:43:58</t>
+        </is>
+      </c>
+      <c r="B2882" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2882" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2882" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2882" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:05</t>
+        </is>
+      </c>
+      <c r="B2883" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2883" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2883" t="n">
+        <v>44</v>
+      </c>
+      <c r="E2883" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:09</t>
+        </is>
+      </c>
+      <c r="B2884" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2884" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2884" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2884" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:13</t>
+        </is>
+      </c>
+      <c r="B2885" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2885" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2885" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2885" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:18</t>
+        </is>
+      </c>
+      <c r="B2886" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2886" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2886" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2886" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:21</t>
+        </is>
+      </c>
+      <c r="B2887" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2887" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2887" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2887" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:24</t>
+        </is>
+      </c>
+      <c r="B2888" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2888" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2888" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2888" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:27</t>
+        </is>
+      </c>
+      <c r="B2889" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2889" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2889" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2889" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:30</t>
+        </is>
+      </c>
+      <c r="B2890" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2890" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2890" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2890" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:36</t>
+        </is>
+      </c>
+      <c r="B2891" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2891" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2891" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2891" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:38</t>
+        </is>
+      </c>
+      <c r="B2892" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2892" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2892" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2892" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:39</t>
+        </is>
+      </c>
+      <c r="B2893" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2893" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2893" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2893" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:41</t>
+        </is>
+      </c>
+      <c r="B2894" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2894" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2894" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2894" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:44</t>
+        </is>
+      </c>
+      <c r="B2895" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2895" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2895" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2895" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:46</t>
+        </is>
+      </c>
+      <c r="B2896" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2896" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2896" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2896" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:47</t>
+        </is>
+      </c>
+      <c r="B2897" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2897" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2897" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2897" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:44:50</t>
+        </is>
+      </c>
+      <c r="B2898" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2898" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2898" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2898" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:15</t>
+        </is>
+      </c>
+      <c r="B2899" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2899" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2899" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2899" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:18</t>
+        </is>
+      </c>
+      <c r="B2900" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2900" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2900" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2900" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:20</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2901" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2901" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2901" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:22</t>
+        </is>
+      </c>
+      <c r="B2902" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2902" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2902" t="n">
+        <v>64</v>
+      </c>
+      <c r="E2902" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:23</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2903" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2903" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2903" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:25</t>
+        </is>
+      </c>
+      <c r="B2904" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2904" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2904" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2904" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:27</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2905" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2905" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2905" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="A2906" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:29</t>
+        </is>
+      </c>
+      <c r="B2906" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2906" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2906" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2906" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:31</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2907" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2907" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2907" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="A2908" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:33</t>
+        </is>
+      </c>
+      <c r="B2908" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2908" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2908" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2908" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:34</t>
+        </is>
+      </c>
+      <c r="B2909" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2909" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2909" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2909" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2910">
+      <c r="A2910" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:36</t>
+        </is>
+      </c>
+      <c r="B2910" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2910" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2910" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2910" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2911">
+      <c r="A2911" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:38</t>
+        </is>
+      </c>
+      <c r="B2911" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2911" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2911" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2911" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2912">
+      <c r="A2912" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:40</t>
+        </is>
+      </c>
+      <c r="B2912" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2912" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2912" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2912" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2913">
+      <c r="A2913" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:42</t>
+        </is>
+      </c>
+      <c r="B2913" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2913" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2913" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2913" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2914">
+      <c r="A2914" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:43</t>
+        </is>
+      </c>
+      <c r="B2914" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2914" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2914" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2914" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="A2915" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:45</t>
+        </is>
+      </c>
+      <c r="B2915" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2915" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2915" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2915" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="A2916" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:47</t>
+        </is>
+      </c>
+      <c r="B2916" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2916" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2916" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2916" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="A2917" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:49</t>
+        </is>
+      </c>
+      <c r="B2917" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2917" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2917" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2917" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="A2918" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:46:51</t>
+        </is>
+      </c>
+      <c r="B2918" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2918" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2918" t="n">
+        <v>38</v>
+      </c>
+      <c r="E2918" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="A2919" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:14</t>
+        </is>
+      </c>
+      <c r="B2919" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2919" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2919" t="n">
+        <v>43</v>
+      </c>
+      <c r="E2919" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2920">
+      <c r="A2920" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:16</t>
+        </is>
+      </c>
+      <c r="B2920" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2920" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2920" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2920" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:17</t>
+        </is>
+      </c>
+      <c r="B2921" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2921" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2921" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2921" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:19</t>
+        </is>
+      </c>
+      <c r="B2922" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2922" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2922" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2922" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:21</t>
+        </is>
+      </c>
+      <c r="B2923" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2923" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2923" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2923" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:22</t>
+        </is>
+      </c>
+      <c r="B2924" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2924" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2924" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2924" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:24</t>
+        </is>
+      </c>
+      <c r="B2925" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2925" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2925" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2925" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:25</t>
+        </is>
+      </c>
+      <c r="B2926" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2926" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2926" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2926" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="A2927" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:27</t>
+        </is>
+      </c>
+      <c r="B2927" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2927" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2927" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2927" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:29</t>
+        </is>
+      </c>
+      <c r="B2928" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2928" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2928" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2928" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:30</t>
+        </is>
+      </c>
+      <c r="B2929" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2929" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2929" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2929" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:32</t>
+        </is>
+      </c>
+      <c r="B2930" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2930" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2930" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2930" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:34</t>
+        </is>
+      </c>
+      <c r="B2931" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2931" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2931" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2931" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:36</t>
+        </is>
+      </c>
+      <c r="B2932" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2932" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2932" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2932" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="A2933" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:37</t>
+        </is>
+      </c>
+      <c r="B2933" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2933" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2933" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2933" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:39</t>
+        </is>
+      </c>
+      <c r="B2934" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2934" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2934" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2934" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:42</t>
+        </is>
+      </c>
+      <c r="B2935" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2935" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2935" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2935" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:45</t>
+        </is>
+      </c>
+      <c r="B2936" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2936" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2936" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2936" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:49</t>
+        </is>
+      </c>
+      <c r="B2937" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2937" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2937" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2937" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:48:53</t>
+        </is>
+      </c>
+      <c r="B2938" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2938" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2938" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2938" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2939">
+      <c r="A2939" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:16</t>
+        </is>
+      </c>
+      <c r="B2939" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2939" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2939" t="n">
+        <v>1.14187</v>
+      </c>
+      <c r="E2939" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2940">
+      <c r="A2940" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:22</t>
+        </is>
+      </c>
+      <c r="B2940" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2940" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2940" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="E2940" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2941">
+      <c r="A2941" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:25</t>
+        </is>
+      </c>
+      <c r="B2941" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2941" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2941" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="E2941" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2942">
+      <c r="A2942" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:27</t>
+        </is>
+      </c>
+      <c r="B2942" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2942" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2942" t="n">
+        <v>0.8216599999999999</v>
+      </c>
+      <c r="E2942" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2943">
+      <c r="A2943" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:29</t>
+        </is>
+      </c>
+      <c r="B2943" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2943" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2943" t="n">
+        <v>144.692</v>
+      </c>
+      <c r="E2943" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2944">
+      <c r="A2944" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:31</t>
+        </is>
+      </c>
+      <c r="B2944" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2944" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2944" t="n">
+        <v>0.93829</v>
+      </c>
+      <c r="E2944" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2945">
+      <c r="A2945" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:33</t>
+        </is>
+      </c>
+      <c r="B2945" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2945" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2945" t="n">
+        <v>1.35138</v>
+      </c>
+      <c r="E2945" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="2946">
+      <c r="A2946" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:34</t>
+        </is>
+      </c>
+      <c r="B2946" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2946" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2946" t="n">
+        <v>1.36909</v>
+      </c>
+      <c r="E2946" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2947">
+      <c r="A2947" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:36</t>
+        </is>
+      </c>
+      <c r="B2947" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2947" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2947" t="n">
+        <v>165.234</v>
+      </c>
+      <c r="E2947" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2948">
+      <c r="A2948" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:38</t>
+        </is>
+      </c>
+      <c r="B2948" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2948" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2948" t="n">
+        <v>0.89233</v>
+      </c>
+      <c r="E2948" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="A2949" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:39</t>
+        </is>
+      </c>
+      <c r="B2949" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2949" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2949" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E2949" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="A2950" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:41</t>
+        </is>
+      </c>
+      <c r="B2950" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2950" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2950" t="n">
+        <v>94.307</v>
+      </c>
+      <c r="E2950" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:43</t>
+        </is>
+      </c>
+      <c r="B2951" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2951" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2951" t="n">
+        <v>0.53552</v>
+      </c>
+      <c r="E2951" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:44</t>
+        </is>
+      </c>
+      <c r="B2952" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2952" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2952" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E2952" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:46</t>
+        </is>
+      </c>
+      <c r="B2953" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2953" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2953" t="n">
+        <v>1.75174</v>
+      </c>
+      <c r="E2953" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:48</t>
+        </is>
+      </c>
+      <c r="B2954" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2954" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2954" t="n">
+        <v>1.11048</v>
+      </c>
+      <c r="E2954" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:51</t>
+        </is>
+      </c>
+      <c r="B2955" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2955" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2955" t="n">
+        <v>1.56328</v>
+      </c>
+      <c r="E2955" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:54</t>
+        </is>
+      </c>
+      <c r="B2956" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2956" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2956" t="n">
+        <v>1.85021</v>
+      </c>
+      <c r="E2956" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:50:56</t>
+        </is>
+      </c>
+      <c r="B2957" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2957" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2957" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="E2957" t="n">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:51:00</t>
+        </is>
+      </c>
+      <c r="B2958" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2958" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2958" t="n">
+        <v>195.543</v>
+      </c>
+      <c r="E2958" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:51:02</t>
+        </is>
+      </c>
+      <c r="B2959" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2959" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2959" t="n">
+        <v>36.5429</v>
+      </c>
+      <c r="E2959" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" t="inlineStr">
+        <is>
+          <t>2025-06-10 21:51:04</t>
+        </is>
+      </c>
+      <c r="B2960" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2960" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2960" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="E2960" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:07</t>
+        </is>
+      </c>
+      <c r="B2961" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2961" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2961" t="n">
+        <v>1.14191</v>
+      </c>
+      <c r="E2961" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:13</t>
+        </is>
+      </c>
+      <c r="B2962" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2962" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2962" t="n">
+        <v>0.60444</v>
+      </c>
+      <c r="E2962" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:16</t>
+        </is>
+      </c>
+      <c r="B2963" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2963" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2963" t="n">
+        <v>0.84499</v>
+      </c>
+      <c r="E2963" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:18</t>
+        </is>
+      </c>
+      <c r="B2964" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2964" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2964" t="n">
+        <v>0.82175</v>
+      </c>
+      <c r="E2964" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="A2965" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:21</t>
+        </is>
+      </c>
+      <c r="B2965" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C2965" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2965" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2965" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:23</t>
+        </is>
+      </c>
+      <c r="B2966" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2966" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2966" t="n">
+        <v>144.726</v>
+      </c>
+      <c r="E2966" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:26</t>
+        </is>
+      </c>
+      <c r="B2967" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2967" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2967" t="n">
+        <v>0.9384400000000001</v>
+      </c>
+      <c r="E2967" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:28</t>
+        </is>
+      </c>
+      <c r="B2968" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2968" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2968" t="n">
+        <v>1.35119</v>
+      </c>
+      <c r="E2968" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:31</t>
+        </is>
+      </c>
+      <c r="B2969" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2969" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2969" t="n">
+        <v>1.36899</v>
+      </c>
+      <c r="E2969" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:35</t>
+        </is>
+      </c>
+      <c r="B2970" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2970" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2970" t="n">
+        <v>165.278</v>
+      </c>
+      <c r="E2970" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:37</t>
+        </is>
+      </c>
+      <c r="B2971" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2971" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2971" t="n">
+        <v>0.89229</v>
+      </c>
+      <c r="E2971" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:39</t>
+        </is>
+      </c>
+      <c r="B2972" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2972" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2972" t="n">
+        <v>0.65171</v>
+      </c>
+      <c r="E2972" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:41</t>
+        </is>
+      </c>
+      <c r="B2973" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2973" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2973" t="n">
+        <v>94.331</v>
+      </c>
+      <c r="E2973" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:42</t>
+        </is>
+      </c>
+      <c r="B2974" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2974" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2974" t="n">
+        <v>0.53559</v>
+      </c>
+      <c r="E2974" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:44</t>
+        </is>
+      </c>
+      <c r="B2975" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2975" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2975" t="n">
+        <v>176.099</v>
+      </c>
+      <c r="E2975" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:46</t>
+        </is>
+      </c>
+      <c r="B2976" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2976" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2976" t="n">
+        <v>1.75177</v>
+      </c>
+      <c r="E2976" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:47</t>
+        </is>
+      </c>
+      <c r="B2977" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2977" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2977" t="n">
+        <v>1.11043</v>
+      </c>
+      <c r="E2977" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:49</t>
+        </is>
+      </c>
+      <c r="B2978" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2978" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2978" t="n">
+        <v>1.56324</v>
+      </c>
+      <c r="E2978" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:51</t>
+        </is>
+      </c>
+      <c r="B2979" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2979" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D2979" t="n">
+        <v>1.84982</v>
+      </c>
+      <c r="E2979" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:52</t>
+        </is>
+      </c>
+      <c r="B2980" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2980" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2980" t="n">
+        <v>3327.2</v>
+      </c>
+      <c r="E2980" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:54</t>
+        </is>
+      </c>
+      <c r="B2981" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2981" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2981" t="n">
+        <v>195.561</v>
+      </c>
+      <c r="E2981" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:57</t>
+        </is>
+      </c>
+      <c r="B2982" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2982" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2982" t="n">
+        <v>36.5392</v>
+      </c>
+      <c r="E2982" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:00:59</t>
+        </is>
+      </c>
+      <c r="B2983" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C2983" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D2983" t="n">
+        <v>1.28634</v>
+      </c>
+      <c r="E2983" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:13</t>
+        </is>
+      </c>
+      <c r="B2984" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2984" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2984" t="n">
+        <v>43</v>
+      </c>
+      <c r="E2984" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:15</t>
+        </is>
+      </c>
+      <c r="B2985" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2985" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2985" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2985" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:17</t>
+        </is>
+      </c>
+      <c r="B2986" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2986" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2986" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2986" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:19</t>
+        </is>
+      </c>
+      <c r="B2987" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2987" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2987" t="n">
+        <v>65</v>
+      </c>
+      <c r="E2987" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:21</t>
+        </is>
+      </c>
+      <c r="B2988" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2988" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2988" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2988" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:23</t>
+        </is>
+      </c>
+      <c r="B2989" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2989" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2989" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2989" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:25</t>
+        </is>
+      </c>
+      <c r="B2990" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2990" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D2990" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2990" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:27</t>
+        </is>
+      </c>
+      <c r="B2991" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2991" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D2991" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2991" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:29</t>
+        </is>
+      </c>
+      <c r="B2992" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2992" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2992" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2992" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:30</t>
+        </is>
+      </c>
+      <c r="B2993" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2993" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2993" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2993" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:33</t>
+        </is>
+      </c>
+      <c r="B2994" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2994" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2994" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2994" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:37</t>
+        </is>
+      </c>
+      <c r="B2995" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2995" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D2995" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2995" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:41</t>
+        </is>
+      </c>
+      <c r="B2996" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2996" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D2996" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2996" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:43</t>
+        </is>
+      </c>
+      <c r="B2997" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2997" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D2997" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2997" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:48</t>
+        </is>
+      </c>
+      <c r="B2998" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2998" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D2998" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2998" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:53</t>
+        </is>
+      </c>
+      <c r="B2999" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C2999" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2999" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2999" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:56</t>
+        </is>
+      </c>
+      <c r="B3000" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3000" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3000" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3000" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:10:59</t>
+        </is>
+      </c>
+      <c r="B3001" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3001" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3001" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3001" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:11:01</t>
+        </is>
+      </c>
+      <c r="B3002" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3002" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3002" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3002" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="A3003" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:11:03</t>
+        </is>
+      </c>
+      <c r="B3003" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3003" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3003" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3003" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="A3004" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:06</t>
+        </is>
+      </c>
+      <c r="B3004" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3004" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3004" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3004" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="A3005" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:09</t>
+        </is>
+      </c>
+      <c r="B3005" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3005" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3005" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3005" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="A3006" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:11</t>
+        </is>
+      </c>
+      <c r="B3006" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3006" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3006" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3006" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="A3007" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:13</t>
+        </is>
+      </c>
+      <c r="B3007" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3007" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3007" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3007" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="A3008" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:16</t>
+        </is>
+      </c>
+      <c r="B3008" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3008" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3008" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3008" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="A3009" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:18</t>
+        </is>
+      </c>
+      <c r="B3009" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3009" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3009" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3009" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="A3010" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:20</t>
+        </is>
+      </c>
+      <c r="B3010" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3010" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3010" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3010" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="A3011" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:22</t>
+        </is>
+      </c>
+      <c r="B3011" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3011" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3011" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3011" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="A3012" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:24</t>
+        </is>
+      </c>
+      <c r="B3012" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3012" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3012" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3012" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="A3013" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:26</t>
+        </is>
+      </c>
+      <c r="B3013" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3013" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3013" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3013" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="A3014" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:28</t>
+        </is>
+      </c>
+      <c r="B3014" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3014" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3014" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3014" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:30</t>
+        </is>
+      </c>
+      <c r="B3015" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3015" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D3015" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3015" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:32</t>
+        </is>
+      </c>
+      <c r="B3016" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3016" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D3016" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3016" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:33</t>
+        </is>
+      </c>
+      <c r="B3017" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3017" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3017" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3017" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:35</t>
+        </is>
+      </c>
+      <c r="B3018" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3018" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3018" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3018" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:37</t>
+        </is>
+      </c>
+      <c r="B3019" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3019" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3019" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3019" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:39</t>
+        </is>
+      </c>
+      <c r="B3020" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3020" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3020" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3020" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:41</t>
+        </is>
+      </c>
+      <c r="B3021" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3021" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3021" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3021" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:43</t>
+        </is>
+      </c>
+      <c r="B3022" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3022" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3022" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3022" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:20:45</t>
+        </is>
+      </c>
+      <c r="B3023" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3023" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3023" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3023" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:24</t>
+        </is>
+      </c>
+      <c r="B3024" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3024" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3024" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3024" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:27</t>
+        </is>
+      </c>
+      <c r="B3025" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3025" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3025" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3025" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:29</t>
+        </is>
+      </c>
+      <c r="B3026" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3026" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3026" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3026" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:31</t>
+        </is>
+      </c>
+      <c r="B3027" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3027" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3027" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3027" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:33</t>
+        </is>
+      </c>
+      <c r="B3028" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3028" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3028" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3028" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:35</t>
+        </is>
+      </c>
+      <c r="B3029" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3029" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3029" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3029" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:39</t>
+        </is>
+      </c>
+      <c r="B3030" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3030" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3030" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3030" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:44</t>
+        </is>
+      </c>
+      <c r="B3031" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3031" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3031" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3031" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:47</t>
+        </is>
+      </c>
+      <c r="B3032" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3032" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3032" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3032" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:51</t>
+        </is>
+      </c>
+      <c r="B3033" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3033" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3033" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3033" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:54</t>
+        </is>
+      </c>
+      <c r="B3034" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3034" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3034" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3034" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:56</t>
+        </is>
+      </c>
+      <c r="B3035" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3035" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D3035" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3035" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:30:58</t>
+        </is>
+      </c>
+      <c r="B3036" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3036" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D3036" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3036" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:00</t>
+        </is>
+      </c>
+      <c r="B3037" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3037" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3037" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3037" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:02</t>
+        </is>
+      </c>
+      <c r="B3038" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3038" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3038" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3038" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:04</t>
+        </is>
+      </c>
+      <c r="B3039" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3039" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3039" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3039" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:06</t>
+        </is>
+      </c>
+      <c r="B3040" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3040" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3040" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3040" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="A3041" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:09</t>
+        </is>
+      </c>
+      <c r="B3041" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3041" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3041" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3041" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:12</t>
+        </is>
+      </c>
+      <c r="B3042" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3042" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3042" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3042" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:31:14</t>
+        </is>
+      </c>
+      <c r="B3043" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3043" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3043" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3043" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:20</t>
+        </is>
+      </c>
+      <c r="B3044" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3044" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3044" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3044" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:25</t>
+        </is>
+      </c>
+      <c r="B3045" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3045" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3045" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3045" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:31</t>
+        </is>
+      </c>
+      <c r="B3046" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3046" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3046" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3046" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:35</t>
+        </is>
+      </c>
+      <c r="B3047" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3047" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3047" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3047" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:37</t>
+        </is>
+      </c>
+      <c r="B3048" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3048" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3048" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3048" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:39</t>
+        </is>
+      </c>
+      <c r="B3049" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3049" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3049" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3049" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:41</t>
+        </is>
+      </c>
+      <c r="B3050" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3050" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3050" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3050" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:44</t>
+        </is>
+      </c>
+      <c r="B3051" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3051" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3051" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3051" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:45</t>
+        </is>
+      </c>
+      <c r="B3052" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3052" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3052" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3052" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:47</t>
+        </is>
+      </c>
+      <c r="B3053" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3053" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3053" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3053" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:49</t>
+        </is>
+      </c>
+      <c r="B3054" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3054" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3054" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3054" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:51</t>
+        </is>
+      </c>
+      <c r="B3055" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3055" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D3055" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3055" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="A3056" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:54</t>
+        </is>
+      </c>
+      <c r="B3056" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3056" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D3056" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3056" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:55</t>
+        </is>
+      </c>
+      <c r="B3057" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3057" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3057" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3057" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="A3058" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:57</t>
+        </is>
+      </c>
+      <c r="B3058" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3058" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3058" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3058" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:40:59</t>
+        </is>
+      </c>
+      <c r="B3059" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3059" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3059" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3059" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:41:01</t>
+        </is>
+      </c>
+      <c r="B3060" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3060" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3060" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3060" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:41:03</t>
+        </is>
+      </c>
+      <c r="B3061" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3061" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3061" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3061" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:41:06</t>
+        </is>
+      </c>
+      <c r="B3062" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3062" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3062" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3062" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:41:08</t>
+        </is>
+      </c>
+      <c r="B3063" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3063" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3063" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3063" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:00</t>
+        </is>
+      </c>
+      <c r="B3064" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3064" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3064" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3064" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:03</t>
+        </is>
+      </c>
+      <c r="B3065" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3065" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3065" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3065" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:05</t>
+        </is>
+      </c>
+      <c r="B3066" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3066" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3066" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3066" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:08</t>
+        </is>
+      </c>
+      <c r="B3067" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3067" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3067" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3067" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:10</t>
+        </is>
+      </c>
+      <c r="B3068" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3068" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3068" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3068" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:14</t>
+        </is>
+      </c>
+      <c r="B3069" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3069" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3069" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3069" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:18</t>
+        </is>
+      </c>
+      <c r="B3070" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3070" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3070" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3070" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="A3071" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:26</t>
+        </is>
+      </c>
+      <c r="B3071" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3071" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3071" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3071" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:29</t>
+        </is>
+      </c>
+      <c r="B3072" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3072" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3072" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:33</t>
+        </is>
+      </c>
+      <c r="B3073" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3073" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3073" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3073" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:37</t>
+        </is>
+      </c>
+      <c r="B3074" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3074" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3074" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3074" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:45</t>
+        </is>
+      </c>
+      <c r="B3075" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D3075" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3075" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:48</t>
+        </is>
+      </c>
+      <c r="B3076" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D3076" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3076" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:51</t>
+        </is>
+      </c>
+      <c r="B3077" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3077" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3077" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:53</t>
+        </is>
+      </c>
+      <c r="B3078" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3078" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3078" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:50:56</t>
+        </is>
+      </c>
+      <c r="B3079" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3079" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3079" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3079" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:51:00</t>
+        </is>
+      </c>
+      <c r="B3080" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3080" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3080" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3080" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:51:04</t>
+        </is>
+      </c>
+      <c r="B3081" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3081" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3081" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3081" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:51:07</t>
+        </is>
+      </c>
+      <c r="B3082" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3082" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3082" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3082" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:51:11</t>
+        </is>
+      </c>
+      <c r="B3083" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3083" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3083" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3083" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:27</t>
+        </is>
+      </c>
+      <c r="B3084" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3084" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3084" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3084" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:30</t>
+        </is>
+      </c>
+      <c r="B3085" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3085" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3085" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3085" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:32</t>
+        </is>
+      </c>
+      <c r="B3086" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3086" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3086" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3086" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:35</t>
+        </is>
+      </c>
+      <c r="B3087" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3087" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3087" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3087" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:37</t>
+        </is>
+      </c>
+      <c r="B3088" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3088" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3088" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3088" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:39</t>
+        </is>
+      </c>
+      <c r="B3089" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3089" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3089" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3089" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:40</t>
+        </is>
+      </c>
+      <c r="B3090" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3090" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3090" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3090" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:42</t>
+        </is>
+      </c>
+      <c r="B3091" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3091" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3091" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3091" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:44</t>
+        </is>
+      </c>
+      <c r="B3092" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3092" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3092" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3092" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:48</t>
+        </is>
+      </c>
+      <c r="B3093" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3093" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3093" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3093" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:51</t>
+        </is>
+      </c>
+      <c r="B3094" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3094" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3094" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3094" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:53</t>
+        </is>
+      </c>
+      <c r="B3095" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3095" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3095" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3095" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:00:59</t>
+        </is>
+      </c>
+      <c r="B3096" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3096" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3096" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3096" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:02</t>
+        </is>
+      </c>
+      <c r="B3097" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3097" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3097" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3097" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:05</t>
+        </is>
+      </c>
+      <c r="B3098" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3098" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D3098" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3098" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:08</t>
+        </is>
+      </c>
+      <c r="B3099" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3099" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3099" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3099" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:12</t>
+        </is>
+      </c>
+      <c r="B3100" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3100" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D3100" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3100" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:15</t>
+        </is>
+      </c>
+      <c r="B3101" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3101" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3101" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3101" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:18</t>
+        </is>
+      </c>
+      <c r="B3102" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3102" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3102" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:20</t>
+        </is>
+      </c>
+      <c r="B3103" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3103" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3103" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:22</t>
+        </is>
+      </c>
+      <c r="B3104" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3104" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3104" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:01:25</t>
+        </is>
+      </c>
+      <c r="B3105" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3105" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3105" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3105" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:23</t>
+        </is>
+      </c>
+      <c r="B3106" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3106" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3106" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3106" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:25</t>
+        </is>
+      </c>
+      <c r="B3107" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3107" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3107" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3107" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:28</t>
+        </is>
+      </c>
+      <c r="B3108" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3108" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3108" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3108" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:32</t>
+        </is>
+      </c>
+      <c r="B3109" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3109" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3109" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3109" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:35</t>
+        </is>
+      </c>
+      <c r="B3110" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3110" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3110" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3110" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:41</t>
+        </is>
+      </c>
+      <c r="B3111" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3111" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3111" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3111" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:44</t>
+        </is>
+      </c>
+      <c r="B3112" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3112" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3112" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3112" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:46</t>
+        </is>
+      </c>
+      <c r="B3113" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3113" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3113" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3113" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:49</t>
+        </is>
+      </c>
+      <c r="B3114" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3114" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3114" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3114" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:10:55</t>
+        </is>
+      </c>
+      <c r="B3115" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3115" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D3115" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3115" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:00</t>
+        </is>
+      </c>
+      <c r="B3116" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3116" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3116" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3116" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:04</t>
+        </is>
+      </c>
+      <c r="B3117" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3117" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3117" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3117" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:08</t>
+        </is>
+      </c>
+      <c r="B3118" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3118" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3118" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3118" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:10</t>
+        </is>
+      </c>
+      <c r="B3119" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3119" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3119" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3119" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:12</t>
+        </is>
+      </c>
+      <c r="B3120" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3120" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D3120" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3120" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:14</t>
+        </is>
+      </c>
+      <c r="B3121" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3121" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3121" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3121" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:16</t>
+        </is>
+      </c>
+      <c r="B3122" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3122" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D3122" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3122" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:20</t>
+        </is>
+      </c>
+      <c r="B3123" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3123" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D3123" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3123" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:23</t>
+        </is>
+      </c>
+      <c r="B3124" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3124" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3124" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3124" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:26</t>
+        </is>
+      </c>
+      <c r="B3125" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3125" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3125" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3125" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:29</t>
+        </is>
+      </c>
+      <c r="B3126" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3126" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3126" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:11:31</t>
+        </is>
+      </c>
+      <c r="B3127" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3127" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D3127" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3127" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:20:21</t>
+        </is>
+      </c>
+      <c r="B3128" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C3128" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3128" t="n">
+        <v>3326.58</v>
+      </c>
+      <c r="E3128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F3128" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:20:23</t>
+        </is>
+      </c>
+      <c r="B3129" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C3129" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3129" t="n">
+        <v>36.5337</v>
+      </c>
+      <c r="E3129" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3129" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:20:25</t>
+        </is>
+      </c>
+      <c r="B3130" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C3130" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3130" t="n">
+        <v>3329.66</v>
+      </c>
+      <c r="E3130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F3130" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:20:27</t>
+        </is>
+      </c>
+      <c r="B3131" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C3131" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3131" t="n">
+        <v>36.2061</v>
+      </c>
+      <c r="E3131" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3131" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:05</t>
+        </is>
+      </c>
+      <c r="B3132" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3132" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3132" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3132" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:08</t>
+        </is>
+      </c>
+      <c r="B3133" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3133" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3133" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3133" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:11</t>
+        </is>
+      </c>
+      <c r="B3134" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3134" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D3134" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3134" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:13</t>
+        </is>
+      </c>
+      <c r="B3135" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3135" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3135" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3135" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:15</t>
+        </is>
+      </c>
+      <c r="B3136" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3136" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D3136" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3136" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:18</t>
+        </is>
+      </c>
+      <c r="B3137" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3137" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D3137" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3137" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="inlineStr">
+        <is>
+          <t>2025-06-10 23:30:20</t>
+        </is>
+      </c>
+      <c r="B3138" t="inlineStr">
+        <is>
+          <t>CCI_STOCH_LOG</t>
+        </is>
+      </c>
+      <c r="C3138" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3138" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3138" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3138" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alligator_data_2.0.xlsx
+++ b/alligator_data_2.0.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4136"/>
+  <dimension ref="A1:F4357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -96744,7 +96744,6194 @@
       <c r="E4136" t="n">
         <v>4</v>
       </c>
-      <c r="F4136" t="inlineStr"/>
+    </row>
+    <row r="4137">
+      <c r="A4137" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:20:20</t>
+        </is>
+      </c>
+      <c r="B4137" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4137" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4137" t="n">
+        <v>3327.63</v>
+      </c>
+      <c r="E4137" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4137" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4138">
+      <c r="A4138" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:20:22</t>
+        </is>
+      </c>
+      <c r="B4138" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4138" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4138" t="n">
+        <v>36.5451</v>
+      </c>
+      <c r="E4138" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4138" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4139">
+      <c r="A4139" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:20:24</t>
+        </is>
+      </c>
+      <c r="B4139" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4139" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4139" t="n">
+        <v>3329.83</v>
+      </c>
+      <c r="E4139" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4139" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4140">
+      <c r="A4140" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:20:26</t>
+        </is>
+      </c>
+      <c r="B4140" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4140" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4140" t="n">
+        <v>36.2795</v>
+      </c>
+      <c r="E4140" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4140" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4141">
+      <c r="A4141" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:30:30</t>
+        </is>
+      </c>
+      <c r="B4141" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4141" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4141" t="n">
+        <v>3327.63</v>
+      </c>
+      <c r="E4141" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4141" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4142">
+      <c r="A4142" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:30:32</t>
+        </is>
+      </c>
+      <c r="B4142" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4142" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4142" t="n">
+        <v>36.5451</v>
+      </c>
+      <c r="E4142" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4142" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4143">
+      <c r="A4143" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:30:34</t>
+        </is>
+      </c>
+      <c r="B4143" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4143" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4143" t="n">
+        <v>3329.83</v>
+      </c>
+      <c r="E4143" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4143" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4144">
+      <c r="A4144" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:30:36</t>
+        </is>
+      </c>
+      <c r="B4144" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4144" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4144" t="n">
+        <v>36.2795</v>
+      </c>
+      <c r="E4144" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4144" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4145">
+      <c r="A4145" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:40:00</t>
+        </is>
+      </c>
+      <c r="B4145" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4145" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4145" t="n">
+        <v>3327.63</v>
+      </c>
+      <c r="E4145" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4145" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4146">
+      <c r="A4146" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:40:03</t>
+        </is>
+      </c>
+      <c r="B4146" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4146" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4146" t="n">
+        <v>36.5451</v>
+      </c>
+      <c r="E4146" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4146" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4147">
+      <c r="A4147" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:40:05</t>
+        </is>
+      </c>
+      <c r="B4147" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4147" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4147" t="n">
+        <v>3329.83</v>
+      </c>
+      <c r="E4147" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4147" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4148">
+      <c r="A4148" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:40:08</t>
+        </is>
+      </c>
+      <c r="B4148" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4148" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4148" t="n">
+        <v>36.2795</v>
+      </c>
+      <c r="E4148" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4148" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4149">
+      <c r="A4149" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:50:15</t>
+        </is>
+      </c>
+      <c r="B4149" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4149" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4149" t="n">
+        <v>3327.63</v>
+      </c>
+      <c r="E4149" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4149" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4150">
+      <c r="A4150" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:50:25</t>
+        </is>
+      </c>
+      <c r="B4150" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4150" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4150" t="n">
+        <v>36.5451</v>
+      </c>
+      <c r="E4150" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4150" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4151">
+      <c r="A4151" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:50:39</t>
+        </is>
+      </c>
+      <c r="B4151" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4151" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4151" t="n">
+        <v>3329.83</v>
+      </c>
+      <c r="E4151" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4151" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4152">
+      <c r="A4152" t="inlineStr">
+        <is>
+          <t>2025-06-11 07:50:46</t>
+        </is>
+      </c>
+      <c r="B4152" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4152" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4152" t="n">
+        <v>36.2795</v>
+      </c>
+      <c r="E4152" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4152" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4153">
+      <c r="A4153" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:00:11</t>
+        </is>
+      </c>
+      <c r="B4153" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4153" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4153" t="n">
+        <v>3329.04</v>
+      </c>
+      <c r="E4153" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4153" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4154">
+      <c r="A4154" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:00:14</t>
+        </is>
+      </c>
+      <c r="B4154" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4154" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4154" t="n">
+        <v>36.5483</v>
+      </c>
+      <c r="E4154" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4154" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4155">
+      <c r="A4155" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:00:16</t>
+        </is>
+      </c>
+      <c r="B4155" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4155" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4155" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4155" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4155" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4156">
+      <c r="A4156" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:00:19</t>
+        </is>
+      </c>
+      <c r="B4156" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4156" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4156" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4156" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4156" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4157">
+      <c r="A4157" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:10:23</t>
+        </is>
+      </c>
+      <c r="B4157" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4157" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4157" t="n">
+        <v>3329.04</v>
+      </c>
+      <c r="E4157" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4157" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4158">
+      <c r="A4158" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:10:25</t>
+        </is>
+      </c>
+      <c r="B4158" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4158" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4158" t="n">
+        <v>36.5483</v>
+      </c>
+      <c r="E4158" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4158" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4159">
+      <c r="A4159" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:10:27</t>
+        </is>
+      </c>
+      <c r="B4159" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4159" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4159" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4159" t="n">
+        <v>29</v>
+      </c>
+      <c r="F4159" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4160">
+      <c r="A4160" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:10:30</t>
+        </is>
+      </c>
+      <c r="B4160" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4160" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4160" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4160" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4160" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4161">
+      <c r="A4161" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:20:34</t>
+        </is>
+      </c>
+      <c r="B4161" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4161" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4161" t="n">
+        <v>3329.04</v>
+      </c>
+      <c r="E4161" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4161" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4162">
+      <c r="A4162" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:20:36</t>
+        </is>
+      </c>
+      <c r="B4162" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4162" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4162" t="n">
+        <v>36.5483</v>
+      </c>
+      <c r="E4162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4162" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4163">
+      <c r="A4163" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:20:38</t>
+        </is>
+      </c>
+      <c r="B4163" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4163" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4163" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4163" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4163" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4164">
+      <c r="A4164" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:20:40</t>
+        </is>
+      </c>
+      <c r="B4164" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4164" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4164" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4164" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4164" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4165">
+      <c r="A4165" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:30:04</t>
+        </is>
+      </c>
+      <c r="B4165" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4165" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4165" t="n">
+        <v>3329.04</v>
+      </c>
+      <c r="E4165" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4165" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4166">
+      <c r="A4166" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:30:07</t>
+        </is>
+      </c>
+      <c r="B4166" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4166" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4166" t="n">
+        <v>36.5483</v>
+      </c>
+      <c r="E4166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4166" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4167">
+      <c r="A4167" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:30:09</t>
+        </is>
+      </c>
+      <c r="B4167" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4167" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4167" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4167" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4167" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4168">
+      <c r="A4168" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:30:11</t>
+        </is>
+      </c>
+      <c r="B4168" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4168" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4168" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4168" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4168" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4169">
+      <c r="A4169" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:40:15</t>
+        </is>
+      </c>
+      <c r="B4169" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4169" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4169" t="n">
+        <v>3329.04</v>
+      </c>
+      <c r="E4169" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4169" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4170">
+      <c r="A4170" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:40:18</t>
+        </is>
+      </c>
+      <c r="B4170" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4170" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4170" t="n">
+        <v>36.5483</v>
+      </c>
+      <c r="E4170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4170" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4171">
+      <c r="A4171" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:40:20</t>
+        </is>
+      </c>
+      <c r="B4171" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4171" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4171" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4171" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4171" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4172">
+      <c r="A4172" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:40:22</t>
+        </is>
+      </c>
+      <c r="B4172" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4172" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4172" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4172" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4172" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4173">
+      <c r="A4173" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:50:26</t>
+        </is>
+      </c>
+      <c r="B4173" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4173" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4173" t="n">
+        <v>3329.04</v>
+      </c>
+      <c r="E4173" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4173" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4174">
+      <c r="A4174" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:50:28</t>
+        </is>
+      </c>
+      <c r="B4174" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4174" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4174" t="n">
+        <v>36.5483</v>
+      </c>
+      <c r="E4174" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4174" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4175">
+      <c r="A4175" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:50:31</t>
+        </is>
+      </c>
+      <c r="B4175" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4175" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4175" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4175" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4175" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4176">
+      <c r="A4176" t="inlineStr">
+        <is>
+          <t>2025-06-11 08:50:33</t>
+        </is>
+      </c>
+      <c r="B4176" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4176" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4176" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4176" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4176" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4177">
+      <c r="A4177" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:00:37</t>
+        </is>
+      </c>
+      <c r="B4177" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4177" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4177" t="n">
+        <v>3330.38</v>
+      </c>
+      <c r="E4177" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4177" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4178">
+      <c r="A4178" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:00:39</t>
+        </is>
+      </c>
+      <c r="B4178" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4178" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4178" t="n">
+        <v>36.5541</v>
+      </c>
+      <c r="E4178" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F4178" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4179">
+      <c r="A4179" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:00:42</t>
+        </is>
+      </c>
+      <c r="B4179" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4179" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4179" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4179" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4179" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4180">
+      <c r="A4180" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:00:44</t>
+        </is>
+      </c>
+      <c r="B4180" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4180" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4180" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4180" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4181">
+      <c r="A4181" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:10:08</t>
+        </is>
+      </c>
+      <c r="B4181" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4181" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4181" t="n">
+        <v>3330.38</v>
+      </c>
+      <c r="E4181" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4181" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4182">
+      <c r="A4182" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:10:11</t>
+        </is>
+      </c>
+      <c r="B4182" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4182" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4182" t="n">
+        <v>36.5541</v>
+      </c>
+      <c r="E4182" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F4182" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:10:13</t>
+        </is>
+      </c>
+      <c r="B4183" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4183" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4183" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4183" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4183" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4184">
+      <c r="A4184" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:10:16</t>
+        </is>
+      </c>
+      <c r="B4184" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4184" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4184" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4184" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4185">
+      <c r="A4185" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:20:20</t>
+        </is>
+      </c>
+      <c r="B4185" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4185" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4185" t="n">
+        <v>3330.38</v>
+      </c>
+      <c r="E4185" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4185" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4186">
+      <c r="A4186" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:20:22</t>
+        </is>
+      </c>
+      <c r="B4186" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4186" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4186" t="n">
+        <v>36.5541</v>
+      </c>
+      <c r="E4186" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F4186" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4187">
+      <c r="A4187" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:20:25</t>
+        </is>
+      </c>
+      <c r="B4187" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4187" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4187" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4187" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4187" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4188">
+      <c r="A4188" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:20:28</t>
+        </is>
+      </c>
+      <c r="B4188" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4188" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4188" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4188" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4189">
+      <c r="A4189" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:30:32</t>
+        </is>
+      </c>
+      <c r="B4189" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4189" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4189" t="n">
+        <v>3330.38</v>
+      </c>
+      <c r="E4189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4189" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4190">
+      <c r="A4190" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:30:35</t>
+        </is>
+      </c>
+      <c r="B4190" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4190" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4190" t="n">
+        <v>36.5541</v>
+      </c>
+      <c r="E4190" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4190" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4191">
+      <c r="A4191" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:30:37</t>
+        </is>
+      </c>
+      <c r="B4191" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4191" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4191" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4191" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4191" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4192">
+      <c r="A4192" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:30:39</t>
+        </is>
+      </c>
+      <c r="B4192" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4192" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4192" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4192" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F4192" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4193">
+      <c r="A4193" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:40:03</t>
+        </is>
+      </c>
+      <c r="B4193" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4193" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4193" t="n">
+        <v>3330.38</v>
+      </c>
+      <c r="E4193" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4193" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4194">
+      <c r="A4194" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:40:06</t>
+        </is>
+      </c>
+      <c r="B4194" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4194" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4194" t="n">
+        <v>36.5541</v>
+      </c>
+      <c r="E4194" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F4194" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4195">
+      <c r="A4195" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:40:08</t>
+        </is>
+      </c>
+      <c r="B4195" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4195" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4195" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4195" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4195" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4196">
+      <c r="A4196" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:40:10</t>
+        </is>
+      </c>
+      <c r="B4196" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4196" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4196" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4196" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4196" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4197">
+      <c r="A4197" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:50:14</t>
+        </is>
+      </c>
+      <c r="B4197" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4197" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4197" t="n">
+        <v>3330.38</v>
+      </c>
+      <c r="E4197" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4197" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4198">
+      <c r="A4198" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:50:16</t>
+        </is>
+      </c>
+      <c r="B4198" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4198" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4198" t="n">
+        <v>36.5541</v>
+      </c>
+      <c r="E4198" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F4198" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4199">
+      <c r="A4199" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:50:19</t>
+        </is>
+      </c>
+      <c r="B4199" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4199" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4199" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4199" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4199" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4200">
+      <c r="A4200" t="inlineStr">
+        <is>
+          <t>2025-06-11 09:50:21</t>
+        </is>
+      </c>
+      <c r="B4200" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4200" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4200" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4200" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4200" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4201">
+      <c r="A4201" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:00:25</t>
+        </is>
+      </c>
+      <c r="B4201" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4201" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4201" t="n">
+        <v>3331.48</v>
+      </c>
+      <c r="E4201" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4201" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4202">
+      <c r="A4202" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:00:27</t>
+        </is>
+      </c>
+      <c r="B4202" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4202" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4202" t="n">
+        <v>36.5481</v>
+      </c>
+      <c r="E4202" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4202" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4203">
+      <c r="A4203" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:00:30</t>
+        </is>
+      </c>
+      <c r="B4203" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4203" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4203" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4203" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4203" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4204">
+      <c r="A4204" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:00:33</t>
+        </is>
+      </c>
+      <c r="B4204" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4204" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4204" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4204" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4204" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4205">
+      <c r="A4205" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:10:38</t>
+        </is>
+      </c>
+      <c r="B4205" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4205" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4205" t="n">
+        <v>3331.48</v>
+      </c>
+      <c r="E4205" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4205" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4206">
+      <c r="A4206" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:10:41</t>
+        </is>
+      </c>
+      <c r="B4206" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4206" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4206" t="n">
+        <v>36.5481</v>
+      </c>
+      <c r="E4206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4206" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4207">
+      <c r="A4207" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:10:43</t>
+        </is>
+      </c>
+      <c r="B4207" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4207" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4207" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4207" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4207" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4208">
+      <c r="A4208" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:10:45</t>
+        </is>
+      </c>
+      <c r="B4208" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4208" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4208" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4208" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4208" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4209">
+      <c r="A4209" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:20:09</t>
+        </is>
+      </c>
+      <c r="B4209" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4209" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4209" t="n">
+        <v>3331.48</v>
+      </c>
+      <c r="E4209" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4209" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4210">
+      <c r="A4210" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:20:11</t>
+        </is>
+      </c>
+      <c r="B4210" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4210" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4210" t="n">
+        <v>36.5481</v>
+      </c>
+      <c r="E4210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4210" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4211">
+      <c r="A4211" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:20:14</t>
+        </is>
+      </c>
+      <c r="B4211" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4211" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4211" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4211" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4211" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4212">
+      <c r="A4212" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:20:17</t>
+        </is>
+      </c>
+      <c r="B4212" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4212" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4212" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4212" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4212" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4213">
+      <c r="A4213" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:30:22</t>
+        </is>
+      </c>
+      <c r="B4213" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4213" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4213" t="n">
+        <v>3331.48</v>
+      </c>
+      <c r="E4213" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4213" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4214">
+      <c r="A4214" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:30:24</t>
+        </is>
+      </c>
+      <c r="B4214" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4214" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4214" t="n">
+        <v>36.5481</v>
+      </c>
+      <c r="E4214" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4214" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4215">
+      <c r="A4215" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:30:27</t>
+        </is>
+      </c>
+      <c r="B4215" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4215" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4215" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4215" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4215" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4216">
+      <c r="A4216" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:30:29</t>
+        </is>
+      </c>
+      <c r="B4216" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4216" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4216" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4216" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4216" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4217">
+      <c r="A4217" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:40:33</t>
+        </is>
+      </c>
+      <c r="B4217" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4217" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4217" t="n">
+        <v>3331.48</v>
+      </c>
+      <c r="E4217" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4217" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4218">
+      <c r="A4218" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:40:36</t>
+        </is>
+      </c>
+      <c r="B4218" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4218" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4218" t="n">
+        <v>36.5481</v>
+      </c>
+      <c r="E4218" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4218" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4219">
+      <c r="A4219" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:40:38</t>
+        </is>
+      </c>
+      <c r="B4219" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4219" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4219" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4219" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4219" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4220">
+      <c r="A4220" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:40:40</t>
+        </is>
+      </c>
+      <c r="B4220" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4220" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4220" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4220" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4220" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4221">
+      <c r="A4221" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:50:04</t>
+        </is>
+      </c>
+      <c r="B4221" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4221" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4221" t="n">
+        <v>3331.48</v>
+      </c>
+      <c r="E4221" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4221" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4222">
+      <c r="A4222" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:50:06</t>
+        </is>
+      </c>
+      <c r="B4222" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4222" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4222" t="n">
+        <v>36.5481</v>
+      </c>
+      <c r="E4222" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4222" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4223">
+      <c r="A4223" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:50:09</t>
+        </is>
+      </c>
+      <c r="B4223" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4223" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4223" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4223" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4223" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4224">
+      <c r="A4224" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:50:11</t>
+        </is>
+      </c>
+      <c r="B4224" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4224" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4224" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4224" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4224" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4225">
+      <c r="A4225" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:00:15</t>
+        </is>
+      </c>
+      <c r="B4225" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4225" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4225" t="n">
+        <v>3332.08</v>
+      </c>
+      <c r="E4225" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4225" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4226">
+      <c r="A4226" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:00:18</t>
+        </is>
+      </c>
+      <c r="B4226" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4226" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4226" t="n">
+        <v>36.5379</v>
+      </c>
+      <c r="E4226" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4226" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4227">
+      <c r="A4227" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:00:20</t>
+        </is>
+      </c>
+      <c r="B4227" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4227" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4227" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4227" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4227" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4228">
+      <c r="A4228" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:00:23</t>
+        </is>
+      </c>
+      <c r="B4228" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4228" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4228" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4228" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4228" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4229">
+      <c r="A4229" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:10:27</t>
+        </is>
+      </c>
+      <c r="B4229" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4229" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4229" t="n">
+        <v>3332.08</v>
+      </c>
+      <c r="E4229" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4229" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4230">
+      <c r="A4230" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:10:29</t>
+        </is>
+      </c>
+      <c r="B4230" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4230" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4230" t="n">
+        <v>36.5379</v>
+      </c>
+      <c r="E4230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4230" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4231">
+      <c r="A4231" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:10:32</t>
+        </is>
+      </c>
+      <c r="B4231" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4231" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4231" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4231" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4231" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4232">
+      <c r="A4232" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:10:35</t>
+        </is>
+      </c>
+      <c r="B4232" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4232" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4232" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4232" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4232" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4233">
+      <c r="A4233" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:20:40</t>
+        </is>
+      </c>
+      <c r="B4233" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4233" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4233" t="n">
+        <v>3332.08</v>
+      </c>
+      <c r="E4233" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4233" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4234">
+      <c r="A4234" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:20:42</t>
+        </is>
+      </c>
+      <c r="B4234" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4234" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4234" t="n">
+        <v>36.5379</v>
+      </c>
+      <c r="E4234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4234" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4235">
+      <c r="A4235" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:20:44</t>
+        </is>
+      </c>
+      <c r="B4235" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4235" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4235" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4235" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4235" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4236">
+      <c r="A4236" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:20:47</t>
+        </is>
+      </c>
+      <c r="B4236" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4236" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4236" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4236" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4236" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4237">
+      <c r="A4237" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:30:11</t>
+        </is>
+      </c>
+      <c r="B4237" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4237" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4237" t="n">
+        <v>3332.08</v>
+      </c>
+      <c r="E4237" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4237" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4238">
+      <c r="A4238" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:30:14</t>
+        </is>
+      </c>
+      <c r="B4238" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4238" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4238" t="n">
+        <v>36.5379</v>
+      </c>
+      <c r="E4238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4238" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:30:16</t>
+        </is>
+      </c>
+      <c r="B4239" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4239" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4239" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4239" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4239" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:30:19</t>
+        </is>
+      </c>
+      <c r="B4240" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4240" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4240" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4240" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4240" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:40:24</t>
+        </is>
+      </c>
+      <c r="B4241" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4241" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4241" t="n">
+        <v>3332.08</v>
+      </c>
+      <c r="E4241" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4241" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4242">
+      <c r="A4242" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:40:26</t>
+        </is>
+      </c>
+      <c r="B4242" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4242" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4242" t="n">
+        <v>36.5379</v>
+      </c>
+      <c r="E4242" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4242" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4243">
+      <c r="A4243" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:40:28</t>
+        </is>
+      </c>
+      <c r="B4243" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4243" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4243" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4243" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4243" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4244">
+      <c r="A4244" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:40:31</t>
+        </is>
+      </c>
+      <c r="B4244" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4244" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4244" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4244" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4244" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4245">
+      <c r="A4245" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:50:35</t>
+        </is>
+      </c>
+      <c r="B4245" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4245" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4245" t="n">
+        <v>3332.08</v>
+      </c>
+      <c r="E4245" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4245" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4246">
+      <c r="A4246" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:50:38</t>
+        </is>
+      </c>
+      <c r="B4246" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4246" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4246" t="n">
+        <v>36.5379</v>
+      </c>
+      <c r="E4246" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4246" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:50:40</t>
+        </is>
+      </c>
+      <c r="B4247" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4247" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4247" t="n">
+        <v>3329.24</v>
+      </c>
+      <c r="E4247" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4247" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4248">
+      <c r="A4248" t="inlineStr">
+        <is>
+          <t>2025-06-11 11:50:43</t>
+        </is>
+      </c>
+      <c r="B4248" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4248" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4248" t="n">
+        <v>36.3138</v>
+      </c>
+      <c r="E4248" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F4248" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:00:07</t>
+        </is>
+      </c>
+      <c r="B4249" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4249" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4249" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4249" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4249" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:00:10</t>
+        </is>
+      </c>
+      <c r="B4250" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4250" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4250" t="n">
+        <v>36.5348</v>
+      </c>
+      <c r="E4250" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F4250" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:00:12</t>
+        </is>
+      </c>
+      <c r="B4251" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4251" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4251" t="n">
+        <v>3329.94</v>
+      </c>
+      <c r="E4251" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4251" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:00:14</t>
+        </is>
+      </c>
+      <c r="B4252" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4252" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4252" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4252" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F4252" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4253">
+      <c r="A4253" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:10:19</t>
+        </is>
+      </c>
+      <c r="B4253" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4253" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4253" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4253" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4253" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4254">
+      <c r="A4254" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:10:21</t>
+        </is>
+      </c>
+      <c r="B4254" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4254" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4254" t="n">
+        <v>36.5348</v>
+      </c>
+      <c r="E4254" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4254" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4255">
+      <c r="A4255" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:10:23</t>
+        </is>
+      </c>
+      <c r="B4255" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4255" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4255" t="n">
+        <v>3329.94</v>
+      </c>
+      <c r="E4255" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4255" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4256">
+      <c r="A4256" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:10:26</t>
+        </is>
+      </c>
+      <c r="B4256" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4256" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4256" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4256" t="n">
+        <v>-38</v>
+      </c>
+      <c r="F4256" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4257">
+      <c r="A4257" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:20:30</t>
+        </is>
+      </c>
+      <c r="B4257" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4257" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4257" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4257" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4257" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4258">
+      <c r="A4258" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:20:32</t>
+        </is>
+      </c>
+      <c r="B4258" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4258" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4258" t="n">
+        <v>36.5348</v>
+      </c>
+      <c r="E4258" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4258" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4259">
+      <c r="A4259" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:20:35</t>
+        </is>
+      </c>
+      <c r="B4259" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4259" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4259" t="n">
+        <v>3329.94</v>
+      </c>
+      <c r="E4259" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4259" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4260">
+      <c r="A4260" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:20:37</t>
+        </is>
+      </c>
+      <c r="B4260" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4260" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4260" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4260" t="n">
+        <v>-38</v>
+      </c>
+      <c r="F4260" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:30:01</t>
+        </is>
+      </c>
+      <c r="B4261" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4261" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4261" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4261" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4261" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:30:05</t>
+        </is>
+      </c>
+      <c r="B4262" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4262" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4262" t="n">
+        <v>36.5348</v>
+      </c>
+      <c r="E4262" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4262" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:30:07</t>
+        </is>
+      </c>
+      <c r="B4263" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4263" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4263" t="n">
+        <v>3329.94</v>
+      </c>
+      <c r="E4263" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4263" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:30:09</t>
+        </is>
+      </c>
+      <c r="B4264" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4264" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4264" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4264" t="n">
+        <v>-38</v>
+      </c>
+      <c r="F4264" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:40:14</t>
+        </is>
+      </c>
+      <c r="B4265" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4265" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4265" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4265" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4265" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:40:17</t>
+        </is>
+      </c>
+      <c r="B4266" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4266" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4266" t="n">
+        <v>36.5348</v>
+      </c>
+      <c r="E4266" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4266" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:40:20</t>
+        </is>
+      </c>
+      <c r="B4267" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4267" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4267" t="n">
+        <v>3329.94</v>
+      </c>
+      <c r="E4267" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4267" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:40:22</t>
+        </is>
+      </c>
+      <c r="B4268" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4268" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4268" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4268" t="n">
+        <v>-38</v>
+      </c>
+      <c r="F4268" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:50:27</t>
+        </is>
+      </c>
+      <c r="B4269" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4269" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4269" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4269" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4269" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4270">
+      <c r="A4270" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:50:29</t>
+        </is>
+      </c>
+      <c r="B4270" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4270" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4270" t="n">
+        <v>36.5348</v>
+      </c>
+      <c r="E4270" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4270" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:50:31</t>
+        </is>
+      </c>
+      <c r="B4271" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4271" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4271" t="n">
+        <v>3329.94</v>
+      </c>
+      <c r="E4271" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4271" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" t="inlineStr">
+        <is>
+          <t>2025-06-11 12:50:33</t>
+        </is>
+      </c>
+      <c r="B4272" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4272" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4272" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4272" t="n">
+        <v>-38</v>
+      </c>
+      <c r="F4272" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:38:43</t>
+        </is>
+      </c>
+      <c r="B4273" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C4273" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4273" t="n">
+        <v>3333.28</v>
+      </c>
+      <c r="E4273" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4273" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:38:45</t>
+        </is>
+      </c>
+      <c r="B4274" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4274" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4274" t="n">
+        <v>36.3755</v>
+      </c>
+      <c r="E4274" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F4274" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:38:48</t>
+        </is>
+      </c>
+      <c r="B4275" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4275" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4275" t="n">
+        <v>3331.25</v>
+      </c>
+      <c r="E4275" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4275" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:38:51</t>
+        </is>
+      </c>
+      <c r="B4276" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4276" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4276" t="n">
+        <v>36.3619</v>
+      </c>
+      <c r="E4276" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F4276" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:38:56</t>
+        </is>
+      </c>
+      <c r="B4277" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C4277" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4277" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F4277" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:40:20</t>
+        </is>
+      </c>
+      <c r="B4278" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4278" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4278" t="n">
+        <v>3335.43</v>
+      </c>
+      <c r="E4278" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F4278" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:40:22</t>
+        </is>
+      </c>
+      <c r="B4279" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4279" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4279" t="n">
+        <v>36.3755</v>
+      </c>
+      <c r="E4279" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F4279" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:40:25</t>
+        </is>
+      </c>
+      <c r="B4280" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4280" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4280" t="n">
+        <v>3331.25</v>
+      </c>
+      <c r="E4280" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4280" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:40:27</t>
+        </is>
+      </c>
+      <c r="B4281" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4281" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4281" t="n">
+        <v>36.3619</v>
+      </c>
+      <c r="E4281" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F4281" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:50:32</t>
+        </is>
+      </c>
+      <c r="B4282" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4282" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4282" t="n">
+        <v>3335.43</v>
+      </c>
+      <c r="E4282" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F4282" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:50:34</t>
+        </is>
+      </c>
+      <c r="B4283" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4283" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4283" t="n">
+        <v>36.3755</v>
+      </c>
+      <c r="E4283" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F4283" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:50:37</t>
+        </is>
+      </c>
+      <c r="B4284" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4284" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4284" t="n">
+        <v>3331.25</v>
+      </c>
+      <c r="E4284" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4284" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" t="inlineStr">
+        <is>
+          <t>2025-06-11 19:50:41</t>
+        </is>
+      </c>
+      <c r="B4285" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4285" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4285" t="n">
+        <v>36.3619</v>
+      </c>
+      <c r="E4285" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F4285" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:00:07</t>
+        </is>
+      </c>
+      <c r="B4286" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4286" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4286" t="n">
+        <v>3335.51</v>
+      </c>
+      <c r="E4286" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F4286" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:00:11</t>
+        </is>
+      </c>
+      <c r="B4287" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4287" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4287" t="n">
+        <v>36.3622</v>
+      </c>
+      <c r="E4287" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F4287" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:00:18</t>
+        </is>
+      </c>
+      <c r="B4288" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C4288" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4288" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F4288" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:00:22</t>
+        </is>
+      </c>
+      <c r="B4289" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4289" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4289" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4289" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F4289" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:00:27</t>
+        </is>
+      </c>
+      <c r="B4290" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4290" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4290" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4290" t="n">
+        <v>-39</v>
+      </c>
+      <c r="F4290" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:10:01</t>
+        </is>
+      </c>
+      <c r="B4291" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4291" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4291" t="n">
+        <v>3335.51</v>
+      </c>
+      <c r="E4291" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F4291" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:10:04</t>
+        </is>
+      </c>
+      <c r="B4292" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4292" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4292" t="n">
+        <v>36.3622</v>
+      </c>
+      <c r="E4292" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F4292" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:10:06</t>
+        </is>
+      </c>
+      <c r="B4293" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4293" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4293" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4293" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F4293" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:10:09</t>
+        </is>
+      </c>
+      <c r="B4294" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4294" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4294" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4294" t="n">
+        <v>-37</v>
+      </c>
+      <c r="F4294" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:20:14</t>
+        </is>
+      </c>
+      <c r="B4295" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4295" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4295" t="n">
+        <v>3335.51</v>
+      </c>
+      <c r="E4295" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F4295" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:20:17</t>
+        </is>
+      </c>
+      <c r="B4296" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4296" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4296" t="n">
+        <v>36.3622</v>
+      </c>
+      <c r="E4296" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F4296" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:20:20</t>
+        </is>
+      </c>
+      <c r="B4297" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4297" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4297" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4297" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F4297" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:20:22</t>
+        </is>
+      </c>
+      <c r="B4298" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4298" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4298" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4298" t="n">
+        <v>-39</v>
+      </c>
+      <c r="F4298" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:30:28</t>
+        </is>
+      </c>
+      <c r="B4299" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4299" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4299" t="n">
+        <v>3335.51</v>
+      </c>
+      <c r="E4299" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4299" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:30:34</t>
+        </is>
+      </c>
+      <c r="B4300" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4300" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4300" t="n">
+        <v>36.3622</v>
+      </c>
+      <c r="E4300" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F4300" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:30:38</t>
+        </is>
+      </c>
+      <c r="B4301" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4301" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4301" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4301" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F4301" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:30:41</t>
+        </is>
+      </c>
+      <c r="B4302" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4302" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4302" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4302" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F4302" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:40:10</t>
+        </is>
+      </c>
+      <c r="B4303" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4303" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4303" t="n">
+        <v>3335.51</v>
+      </c>
+      <c r="E4303" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F4303" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:40:18</t>
+        </is>
+      </c>
+      <c r="B4304" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4304" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4304" t="n">
+        <v>36.3622</v>
+      </c>
+      <c r="E4304" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F4304" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:40:24</t>
+        </is>
+      </c>
+      <c r="B4305" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4305" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4305" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4305" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F4305" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:40:29</t>
+        </is>
+      </c>
+      <c r="B4306" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4306" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4306" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4306" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4306" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:50:38</t>
+        </is>
+      </c>
+      <c r="B4307" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4307" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4307" t="n">
+        <v>3335.51</v>
+      </c>
+      <c r="E4307" t="n">
+        <v>-22</v>
+      </c>
+      <c r="F4307" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:50:46</t>
+        </is>
+      </c>
+      <c r="B4308" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4308" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4308" t="n">
+        <v>36.3622</v>
+      </c>
+      <c r="E4308" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F4308" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:50:54</t>
+        </is>
+      </c>
+      <c r="B4309" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4309" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4309" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4309" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F4309" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" t="inlineStr">
+        <is>
+          <t>2025-06-11 20:51:03</t>
+        </is>
+      </c>
+      <c r="B4310" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4310" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4310" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4310" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4310" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:00:33</t>
+        </is>
+      </c>
+      <c r="B4311" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4311" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4311" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4311" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4311" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:00:39</t>
+        </is>
+      </c>
+      <c r="B4312" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C4312" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4312" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4312" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:00:43</t>
+        </is>
+      </c>
+      <c r="B4313" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4313" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4313" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4313" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F4313" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:00:47</t>
+        </is>
+      </c>
+      <c r="B4314" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4314" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4314" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4314" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F4314" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:00:50</t>
+        </is>
+      </c>
+      <c r="B4315" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4315" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4315" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4315" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4315" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:05:36</t>
+        </is>
+      </c>
+      <c r="B4316" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C4316" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4316" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4316" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F4316" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:10:20</t>
+        </is>
+      </c>
+      <c r="B4317" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4317" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4317" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4317" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4317" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:10:23</t>
+        </is>
+      </c>
+      <c r="B4318" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4318" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4318" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4318" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F4318" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:10:29</t>
+        </is>
+      </c>
+      <c r="B4319" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4319" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4319" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4319" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F4319" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:10:34</t>
+        </is>
+      </c>
+      <c r="B4320" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4320" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4320" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4320" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4320" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:20:00</t>
+        </is>
+      </c>
+      <c r="B4321" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4321" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4321" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4321" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4321" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:20:04</t>
+        </is>
+      </c>
+      <c r="B4322" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4322" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4322" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4322" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F4322" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:20:07</t>
+        </is>
+      </c>
+      <c r="B4323" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4323" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4323" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4323" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F4323" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4324">
+      <c r="A4324" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:20:09</t>
+        </is>
+      </c>
+      <c r="B4324" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4324" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4324" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4324" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F4324" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4325">
+      <c r="A4325" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:30:20</t>
+        </is>
+      </c>
+      <c r="B4325" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4325" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4325" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4325" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4325" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4326">
+      <c r="A4326" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:30:28</t>
+        </is>
+      </c>
+      <c r="B4326" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4326" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4326" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4326" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4326" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4327">
+      <c r="A4327" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:30:33</t>
+        </is>
+      </c>
+      <c r="B4327" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4327" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4327" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4327" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F4327" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4328">
+      <c r="A4328" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:30:37</t>
+        </is>
+      </c>
+      <c r="B4328" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4328" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4328" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4328" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4328" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4329">
+      <c r="A4329" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:40:04</t>
+        </is>
+      </c>
+      <c r="B4329" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4329" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4329" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4329" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4329" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4330">
+      <c r="A4330" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:40:09</t>
+        </is>
+      </c>
+      <c r="B4330" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4330" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4330" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4330" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4330" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4331">
+      <c r="A4331" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:40:16</t>
+        </is>
+      </c>
+      <c r="B4331" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4331" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4331" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4331" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4331" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4332">
+      <c r="A4332" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:40:21</t>
+        </is>
+      </c>
+      <c r="B4332" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4332" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4332" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4332" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4332" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4333">
+      <c r="A4333" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:50:32</t>
+        </is>
+      </c>
+      <c r="B4333" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4333" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4333" t="n">
+        <v>3334.97</v>
+      </c>
+      <c r="E4333" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4333" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4334">
+      <c r="A4334" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:50:44</t>
+        </is>
+      </c>
+      <c r="B4334" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4334" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4334" t="n">
+        <v>36.3448</v>
+      </c>
+      <c r="E4334" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F4334" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4335">
+      <c r="A4335" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:50:50</t>
+        </is>
+      </c>
+      <c r="B4335" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4335" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4335" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4335" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4335" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4336">
+      <c r="A4336" t="inlineStr">
+        <is>
+          <t>2025-06-11 21:50:59</t>
+        </is>
+      </c>
+      <c r="B4336" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4336" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4336" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4336" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4336" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4337">
+      <c r="A4337" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:00:27</t>
+        </is>
+      </c>
+      <c r="B4337" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4337" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4337" t="n">
+        <v>3333.75</v>
+      </c>
+      <c r="E4337" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4337" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4338">
+      <c r="A4338" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:00:30</t>
+        </is>
+      </c>
+      <c r="B4338" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C4338" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4338" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4338" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4339">
+      <c r="A4339" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:00:34</t>
+        </is>
+      </c>
+      <c r="B4339" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4339" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4339" t="n">
+        <v>36.3177</v>
+      </c>
+      <c r="E4339" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F4339" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4340">
+      <c r="A4340" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:00:42</t>
+        </is>
+      </c>
+      <c r="B4340" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4340" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4340" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4340" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4340" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4341">
+      <c r="A4341" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:00:50</t>
+        </is>
+      </c>
+      <c r="B4341" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4341" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4341" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4341" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4341" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4342">
+      <c r="A4342" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:10:17</t>
+        </is>
+      </c>
+      <c r="B4342" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4342" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4342" t="n">
+        <v>3333.75</v>
+      </c>
+      <c r="E4342" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4342" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4343">
+      <c r="A4343" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:10:21</t>
+        </is>
+      </c>
+      <c r="B4343" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4343" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4343" t="n">
+        <v>36.3177</v>
+      </c>
+      <c r="E4343" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F4343" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4344">
+      <c r="A4344" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:10:25</t>
+        </is>
+      </c>
+      <c r="B4344" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4344" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4344" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4344" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4344" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4345">
+      <c r="A4345" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:10:33</t>
+        </is>
+      </c>
+      <c r="B4345" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4345" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4345" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4345" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4345" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4346">
+      <c r="A4346" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:20:00</t>
+        </is>
+      </c>
+      <c r="B4346" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4346" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4346" t="n">
+        <v>3333.75</v>
+      </c>
+      <c r="E4346" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4346" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4347">
+      <c r="A4347" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:20:03</t>
+        </is>
+      </c>
+      <c r="B4347" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4347" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4347" t="n">
+        <v>36.3177</v>
+      </c>
+      <c r="E4347" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F4347" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4348">
+      <c r="A4348" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:20:05</t>
+        </is>
+      </c>
+      <c r="B4348" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4348" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4348" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4348" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4348" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4349">
+      <c r="A4349" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:20:08</t>
+        </is>
+      </c>
+      <c r="B4349" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4349" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4349" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4349" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4349" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4350">
+      <c r="A4350" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:30:15</t>
+        </is>
+      </c>
+      <c r="B4350" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4350" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4350" t="n">
+        <v>3333.75</v>
+      </c>
+      <c r="E4350" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4350" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4351">
+      <c r="A4351" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:30:18</t>
+        </is>
+      </c>
+      <c r="B4351" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4351" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4351" t="n">
+        <v>36.3177</v>
+      </c>
+      <c r="E4351" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F4351" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4352">
+      <c r="A4352" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:30:21</t>
+        </is>
+      </c>
+      <c r="B4352" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4352" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4352" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4352" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4352" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4353">
+      <c r="A4353" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:30:25</t>
+        </is>
+      </c>
+      <c r="B4353" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4353" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4353" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4353" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4353" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4354">
+      <c r="A4354" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:40:33</t>
+        </is>
+      </c>
+      <c r="B4354" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4354" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4354" t="n">
+        <v>3333.75</v>
+      </c>
+      <c r="E4354" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4354" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4355">
+      <c r="A4355" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:40:40</t>
+        </is>
+      </c>
+      <c r="B4355" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4355" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4355" t="n">
+        <v>36.3177</v>
+      </c>
+      <c r="E4355" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F4355" t="inlineStr">
+        <is>
+          <t>16385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4356">
+      <c r="A4356" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:40:46</t>
+        </is>
+      </c>
+      <c r="B4356" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4356" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4356" t="n">
+        <v>3332.75</v>
+      </c>
+      <c r="E4356" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4356" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
+    </row>
+    <row r="4357">
+      <c r="A4357" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:40:51</t>
+        </is>
+      </c>
+      <c r="B4357" t="inlineStr">
+        <is>
+          <t>ALLIGATOR_LOG</t>
+        </is>
+      </c>
+      <c r="C4357" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D4357" t="n">
+        <v>36.3517</v>
+      </c>
+      <c r="E4357" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4357" t="inlineStr">
+        <is>
+          <t>16388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
